--- a/Courses/Term 3/QAM-III/Case Studies/921 DATA - INDIA warehouse location gravity.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/921 DATA - INDIA warehouse location gravity.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/OR - NEW - Divs AD/DAY 12 NLP - Pricing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA41302-39B8-B64D-8EBD-6E5F4A3357F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348F855D-6046-417B-89F3-8EECC50AB59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-580" yWindow="740" windowWidth="29400" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="140000"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
   <si>
     <r>
       <t xml:space="preserve">A retail chain wants to start a </t>
@@ -95,12 +106,36 @@
   <si>
     <t>Y-Axis</t>
   </si>
+  <si>
+    <t>SOLUTION</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>Location x</t>
+  </si>
+  <si>
+    <t>Location y</t>
+  </si>
+  <si>
+    <t>Demand x</t>
+  </si>
+  <si>
+    <t>Demand y</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -137,6 +172,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -158,7 +201,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,11 +209,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -188,8 +241,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1138,10 +1193,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:R51"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1157,7 +1212,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1165,28 +1220,28 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1195,7 +1250,7 @@
       </c>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>9</v>
       </c>
@@ -1204,7 +1259,7 @@
       </c>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>10</v>
       </c>
@@ -1213,7 +1268,7 @@
       </c>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>11</v>
       </c>
@@ -1222,7 +1277,7 @@
       </c>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1231,7 +1286,7 @@
       </c>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -1240,16 +1295,16 @@
       </c>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="6" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1313,7 @@
       </c>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>8</v>
       </c>
@@ -1270,7 +1325,7 @@
       </c>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>9</v>
       </c>
@@ -1282,7 +1337,7 @@
       </c>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>10</v>
       </c>
@@ -1294,7 +1349,7 @@
       </c>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>11</v>
       </c>
@@ -1306,7 +1361,7 @@
       </c>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>12</v>
       </c>
@@ -1318,7 +1373,7 @@
       </c>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>13</v>
       </c>
@@ -1336,66 +1391,241 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M41" s="5" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>50</v>
+      </c>
+      <c r="D45" s="3">
+        <v>-6</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6</v>
+      </c>
+      <c r="F45">
+        <f>D45*C45</f>
+        <v>-300</v>
+      </c>
+      <c r="G45">
+        <f>E45*C45</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>60</v>
+      </c>
+      <c r="D46" s="3">
+        <v>7</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8</v>
+      </c>
+      <c r="F46">
+        <f t="shared" ref="F46:F50" si="0">D46*C46</f>
+        <v>420</v>
+      </c>
+      <c r="G46">
+        <f t="shared" ref="G46:G50" si="1">E46*C46</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <v>30</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <v>45</v>
+      </c>
+      <c r="D48" s="3">
+        <v>2</v>
+      </c>
+      <c r="E48" s="3">
+        <v>-3</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="1"/>
+        <v>-135</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>20</v>
+      </c>
+      <c r="D49" s="3">
+        <v>-3</v>
+      </c>
+      <c r="E49" s="3">
+        <v>-5</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="1"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50">
+        <v>40</v>
+      </c>
+      <c r="D50" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E50" s="3">
+        <v>-4</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="1"/>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51">
+        <f>SUM(C45:C50)</f>
+        <v>245</v>
+      </c>
+      <c r="F51">
+        <f t="shared" ref="D51:G51" si="2">SUM(F45:F50)</f>
+        <v>110</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="2"/>
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/Courses/Term 3/QAM-III/Case Studies/921 DATA - INDIA warehouse location gravity.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/921 DATA - INDIA warehouse location gravity.xlsx
@@ -8,13 +8,42 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348F855D-6046-417B-89F3-8EECC50AB59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34509EB-7A5C-4553-9043-91CC2720D7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$D$53:$E$53</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$I$51</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <r>
       <t xml:space="preserve">A retail chain wants to start a </t>
@@ -122,13 +151,19 @@
     <t>Location y</t>
   </si>
   <si>
-    <t>Demand x</t>
-  </si>
-  <si>
-    <t>Demand y</t>
-  </si>
-  <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deviation Variables </t>
+  </si>
+  <si>
+    <t>Distance using Deviation Variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance using Deviation Variables </t>
+  </si>
+  <si>
+    <t>Demand Squard</t>
   </si>
 </sst>
 </file>
@@ -181,7 +216,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +232,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -223,25 +270,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
@@ -1193,443 +1256,460 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="11.19921875" style="2"/>
+    <col min="6" max="6" width="37.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="2"/>
+    <col min="8" max="8" width="37.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="11.19921875" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>50</v>
       </c>
-      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>60</v>
       </c>
-      <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>30</v>
       </c>
-      <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>45</v>
       </c>
-      <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>20</v>
       </c>
-      <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>40</v>
       </c>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M16" s="2"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <v>-6</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <v>6</v>
       </c>
-      <c r="M17" s="2"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="4">
         <v>7</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="4">
         <v>8</v>
       </c>
-      <c r="M18" s="2"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="4">
         <v>0</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="4">
         <v>1</v>
       </c>
-      <c r="M19" s="2"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>2</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <v>-3</v>
       </c>
-      <c r="M20" s="2"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>-3</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
         <v>-5</v>
       </c>
-      <c r="M21" s="2"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="4">
         <v>-1</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="4">
         <v>-4</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M22" s="2"/>
-      <c r="R22" s="4" t="s">
+      <c r="R22" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M24" s="2"/>
-    </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M26" s="2"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M27" s="2"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M28" s="2"/>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M29" s="2"/>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M34" s="2"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M35" s="2"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M37" s="2"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M41" s="5" t="s">
+      <c r="M41" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:13" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="10">
+        <v>50</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-6</v>
+      </c>
+      <c r="E45" s="6">
+        <v>6</v>
+      </c>
+      <c r="F45" s="10">
+        <f>SQRT(SUMXMY2(D45:E45,$D$53:$E$53))</f>
+        <v>7.7544846410165507</v>
+      </c>
+      <c r="G45" s="2">
+        <f>F45*C45</f>
+        <v>387.72423205082754</v>
+      </c>
+      <c r="H45" s="2">
+        <f>F45*F45</f>
+        <v>60.132032047761584</v>
+      </c>
+      <c r="I45" s="2">
+        <f>H45*C45</f>
+        <v>3006.6016023880793</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="10">
+        <v>60</v>
+      </c>
+      <c r="D46" s="6">
+        <v>7</v>
+      </c>
+      <c r="E46" s="6">
+        <v>8</v>
+      </c>
+      <c r="F46" s="10">
+        <f>SQRT(SUMXMY2(D46:E46,$D$53:$E$53))</f>
+        <v>9.0930219469826046</v>
+      </c>
+      <c r="G46" s="2">
+        <f>F46*C46</f>
+        <v>545.58131681895622</v>
+      </c>
+      <c r="H46" s="2">
+        <f t="shared" ref="H46:H50" si="0">F46*F46</f>
+        <v>82.68304812830732</v>
+      </c>
+      <c r="I46" s="2">
+        <f t="shared" ref="I46:I50" si="1">H46*C46</f>
+        <v>4960.9828876984393</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="10">
+        <v>30</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0</v>
+      </c>
+      <c r="E47" s="6">
+        <v>1</v>
+      </c>
+      <c r="F47" s="10">
+        <f>SQRT(SUMXMY2(D47:E47,$D$53:$E$53))</f>
+        <v>0.82646759942888581</v>
+      </c>
+      <c r="G47" s="2">
+        <f>F47*C47</f>
+        <v>24.794027982866574</v>
+      </c>
+      <c r="H47" s="2">
+        <f t="shared" si="0"/>
+        <v>0.68304869290574521</v>
+      </c>
+      <c r="I47" s="2">
+        <f t="shared" si="1"/>
+        <v>20.491460787172358</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="10">
+        <v>45</v>
+      </c>
+      <c r="D48" s="6">
+        <v>2</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-3</v>
+      </c>
+      <c r="F48" s="10">
+        <f>SQRT(SUMXMY2(D48:E48,$D$53:$E$53))</f>
+        <v>4.9434956037019449</v>
+      </c>
+      <c r="G48" s="2">
+        <f>F48*C48</f>
+        <v>222.45730216658751</v>
+      </c>
+      <c r="H48" s="2">
+        <f t="shared" si="0"/>
+        <v>24.438148783820456</v>
+      </c>
+      <c r="I48" s="2">
+        <f t="shared" si="1"/>
+        <v>1099.7166952719206</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="10">
+        <v>20</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-3</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-5</v>
+      </c>
+      <c r="F49" s="10">
+        <f>SQRT(SUMXMY2(D49:E49,$D$53:$E$53))</f>
+        <v>7.5301697327382939</v>
+      </c>
+      <c r="G49" s="2">
+        <f>F49*C49</f>
+        <v>150.60339465476588</v>
+      </c>
+      <c r="H49" s="2">
+        <f t="shared" si="0"/>
+        <v>56.703456203847907</v>
+      </c>
+      <c r="I49" s="2">
+        <f t="shared" si="1"/>
+        <v>1134.0691240769581</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="10">
+        <v>40</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-1</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-4</v>
+      </c>
+      <c r="F50" s="10">
+        <f>SQRT(SUMXMY2(D50:E50,$D$53:$E$53))</f>
+        <v>5.87535379998927</v>
+      </c>
+      <c r="G50" s="2">
+        <f>F50*C50</f>
+        <v>235.0141519995708</v>
+      </c>
+      <c r="H50" s="2">
+        <f t="shared" si="0"/>
+        <v>34.519782275048357</v>
+      </c>
+      <c r="I50" s="2">
+        <f t="shared" si="1"/>
+        <v>1380.7912910019343</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B51" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45">
-        <v>50</v>
-      </c>
-      <c r="D45" s="3">
-        <v>-6</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6</v>
-      </c>
-      <c r="F45">
-        <f>D45*C45</f>
-        <v>-300</v>
-      </c>
-      <c r="G45">
-        <f>E45*C45</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46">
-        <v>60</v>
-      </c>
-      <c r="D46" s="3">
-        <v>7</v>
-      </c>
-      <c r="E46" s="3">
-        <v>8</v>
-      </c>
-      <c r="F46">
-        <f t="shared" ref="F46:F50" si="0">D46*C46</f>
-        <v>420</v>
-      </c>
-      <c r="G46">
-        <f t="shared" ref="G46:G50" si="1">E46*C46</f>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47">
-        <v>30</v>
-      </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48">
-        <v>45</v>
-      </c>
-      <c r="D48" s="3">
-        <v>2</v>
-      </c>
-      <c r="E48" s="3">
-        <v>-3</v>
-      </c>
-      <c r="F48">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="1"/>
-        <v>-135</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49">
-        <v>20</v>
-      </c>
-      <c r="D49" s="3">
-        <v>-3</v>
-      </c>
-      <c r="E49" s="3">
-        <v>-5</v>
-      </c>
-      <c r="F49">
-        <f t="shared" si="0"/>
-        <v>-60</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="1"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50">
-        <v>40</v>
-      </c>
-      <c r="D50" s="3">
-        <v>-1</v>
-      </c>
-      <c r="E50" s="3">
-        <v>-4</v>
-      </c>
-      <c r="F50">
-        <f t="shared" si="0"/>
-        <v>-40</v>
-      </c>
-      <c r="G50">
-        <f t="shared" si="1"/>
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51">
+      <c r="C51" s="10">
         <f>SUM(C45:C50)</f>
         <v>245</v>
       </c>
-      <c r="F51">
-        <f t="shared" ref="D51:G51" si="2">SUM(F45:F50)</f>
-        <v>110</v>
-      </c>
-      <c r="G51">
-        <f t="shared" si="2"/>
-        <v>415</v>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10">
+        <f>SUM(G45:G50)</f>
+        <v>1566.1744256735747</v>
+      </c>
+      <c r="H51" s="2">
+        <f>SUM(H45:H50)</f>
+        <v>259.15951613169136</v>
+      </c>
+      <c r="I51" s="2">
+        <f>SUM(I45:I50)</f>
+        <v>11602.653061224504</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="7">
+        <v>0.44897978121417526</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1.6938774019714264</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D54" s="11">
+        <v>5</v>
+      </c>
+      <c r="E54" s="11">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="F45" formulaRange="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
